--- a/work2-ledger-checker/check_report.xlsx
+++ b/work2-ledger-checker/check_report.xlsx
@@ -12,7 +12,12 @@
     <sheet name="属性不一致" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="妥当性エラー" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'サマリ'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'ID差分'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'属性不一致'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'妥当性エラー'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -426,13 +431,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,7 +460,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -511,6 +516,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -518,13 +524,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -601,6 +607,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -608,15 +615,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,6 +708,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -708,14 +716,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -833,5 +841,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/work2-ledger-checker/check_report.xlsx
+++ b/work2-ledger-checker/check_report.xlsx
@@ -515,6 +515,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -606,6 +607,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -707,6 +709,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -840,6 +843,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/work2-ledger-checker/check_report.xlsx
+++ b/work2-ledger-checker/check_report.xlsx
@@ -24,7 +24,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -63,11 +66,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -458,10 +462,8 @@
           <t>チェック実行日</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
+      <c r="B2" s="2" t="n">
+        <v>46257</v>
       </c>
     </row>
     <row r="3">
